--- a/deSousa__2008/deSousa__2008_Suppl.Table5.2_snapshot.xlsx
+++ b/deSousa__2008/deSousa__2008_Suppl.Table5.2_snapshot.xlsx
@@ -1166,13 +1166,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F924443D-2856-454C-9A1C-9AAF4394025A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{292BB13D-05D9-43DE-A6D2-DA30E30B854C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D36B981D-CC86-4EE2-9062-209123AF74C9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0B8BCE9-04F2-428B-A942-626562749817}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAE910C2-C490-46A8-A5A8-FD9CD30FB513}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B5892C33-29D9-4C0E-9BC9-36169D9F3EA8}"/>
 </file>
--- a/deSousa__2008/deSousa__2008_Suppl.Table5.2_snapshot.xlsx
+++ b/deSousa__2008/deSousa__2008_Suppl.Table5.2_snapshot.xlsx
@@ -1166,13 +1166,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{292BB13D-05D9-43DE-A6D2-DA30E30B854C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C210FF2-6F60-4F07-8334-8A621FCA2358}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0B8BCE9-04F2-428B-A942-626562749817}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0E8BFDF-D504-4CEF-B6A4-FC0D725ED756}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B5892C33-29D9-4C0E-9BC9-36169D9F3EA8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{256120C9-3403-4112-A1D1-9F1F58FA2A05}"/>
 </file>
--- a/deSousa__2008/deSousa__2008_Suppl.Table5.2_snapshot.xlsx
+++ b/deSousa__2008/deSousa__2008_Suppl.Table5.2_snapshot.xlsx
@@ -1166,13 +1166,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C210FF2-6F60-4F07-8334-8A621FCA2358}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5709CA91-BCA9-422D-A422-CF1FE337FAF1}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0E8BFDF-D504-4CEF-B6A4-FC0D725ED756}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DED84BC7-6CA1-4E42-B51E-5F1C71B0AD4E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{256120C9-3403-4112-A1D1-9F1F58FA2A05}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1773EB9B-5A9A-402D-A3E0-9B7C553F7349}"/>
 </file>
--- a/deSousa__2008/deSousa__2008_Suppl.Table5.2_snapshot.xlsx
+++ b/deSousa__2008/deSousa__2008_Suppl.Table5.2_snapshot.xlsx
@@ -1166,13 +1166,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5709CA91-BCA9-422D-A422-CF1FE337FAF1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{719D3DF3-557A-40B1-869B-0B45390A7B73}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DED84BC7-6CA1-4E42-B51E-5F1C71B0AD4E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BCD55211-182F-4732-AC71-12CC5E065A0D}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1773EB9B-5A9A-402D-A3E0-9B7C553F7349}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DC3569DA-D2F0-4BE4-8CAF-CE2CC0D5727E}"/>
 </file>
--- a/deSousa__2008/deSousa__2008_Suppl.Table5.2_snapshot.xlsx
+++ b/deSousa__2008/deSousa__2008_Suppl.Table5.2_snapshot.xlsx
@@ -1166,13 +1166,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{719D3DF3-557A-40B1-869B-0B45390A7B73}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D512EA4B-495C-45A6-B5A6-5E37CCFCC49D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BCD55211-182F-4732-AC71-12CC5E065A0D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A7754B1B-181E-4149-9AE2-06996A096383}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DC3569DA-D2F0-4BE4-8CAF-CE2CC0D5727E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8D94834F-C97E-4A03-A7C5-288A994347B7}"/>
 </file>
--- a/deSousa__2008/deSousa__2008_Suppl.Table5.2_snapshot.xlsx
+++ b/deSousa__2008/deSousa__2008_Suppl.Table5.2_snapshot.xlsx
@@ -1166,13 +1166,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D512EA4B-495C-45A6-B5A6-5E37CCFCC49D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ADF55D6D-01BF-4D46-91D7-2E88864E049C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A7754B1B-181E-4149-9AE2-06996A096383}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2B506D3E-CF90-4C7A-B23D-F6F50CC4DD73}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8D94834F-C97E-4A03-A7C5-288A994347B7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E451ECB7-56E8-4006-B45B-F6C6EDA44818}"/>
 </file>
--- a/deSousa__2008/deSousa__2008_Suppl.Table5.2_snapshot.xlsx
+++ b/deSousa__2008/deSousa__2008_Suppl.Table5.2_snapshot.xlsx
@@ -1166,13 +1166,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ADF55D6D-01BF-4D46-91D7-2E88864E049C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B7EB956D-345D-445F-8A1F-EA6D614DB5CD}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2B506D3E-CF90-4C7A-B23D-F6F50CC4DD73}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23955555-137B-4FFE-A6DE-2ED01B4425B3}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E451ECB7-56E8-4006-B45B-F6C6EDA44818}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5E764784-9921-4017-9E13-A70561C8E1F9}"/>
 </file>
--- a/deSousa__2008/deSousa__2008_Suppl.Table5.2_snapshot.xlsx
+++ b/deSousa__2008/deSousa__2008_Suppl.Table5.2_snapshot.xlsx
@@ -1166,13 +1166,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B7EB956D-345D-445F-8A1F-EA6D614DB5CD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EDAF45BD-9E5B-4F65-A914-A4F6D93F4322}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23955555-137B-4FFE-A6DE-2ED01B4425B3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FF5260A-F9A8-48D9-A5D9-40606B058960}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5E764784-9921-4017-9E13-A70561C8E1F9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A77B31C-4182-420F-82C5-4D81841816C9}"/>
 </file>
--- a/deSousa__2008/deSousa__2008_Suppl.Table5.2_snapshot.xlsx
+++ b/deSousa__2008/deSousa__2008_Suppl.Table5.2_snapshot.xlsx
@@ -1166,13 +1166,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EDAF45BD-9E5B-4F65-A914-A4F6D93F4322}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EBEE1EE1-86A2-4226-9C29-CA39E9D519AC}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FF5260A-F9A8-48D9-A5D9-40606B058960}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FDAA6C55-DD93-4BD1-A85C-A0CDB3137893}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A77B31C-4182-420F-82C5-4D81841816C9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{96DF73DE-2B62-4952-BB83-B3427805C945}"/>
 </file>